--- a/Shared/XLS/Buff.xlsx
+++ b/Shared/XLS/Buff.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="11.625" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
@@ -606,8 +606,8 @@
     <col width="36.75" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
     <col width="2.5" customWidth="1" style="8" min="4" max="4"/>
     <col width="150.25" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
-    <col width="9" customWidth="1" style="4" min="6" max="8"/>
-    <col width="9" customWidth="1" style="4" min="9" max="16384"/>
+    <col width="9" customWidth="1" style="4" min="6" max="9"/>
+    <col width="9" customWidth="1" style="4" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="12">
@@ -674,66 +674,78 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="n"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IndependentShared</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>스택마다 독립 인스턴스 + 수명은 공유(쌍검 공속)</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="1" s="12">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="B7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>!Enum</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>ActionBlockType</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="10" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Move</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>이동 불가</t>
-        </is>
-      </c>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>회전 불가</t>
+          <t>Move</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>이동 불가</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="13" t="inlineStr">
         <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>회전 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>일반 공격 불가</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Cast</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>스킬 시전 불가. 진행 중인 시전도 취소</t>
         </is>
@@ -766,8 +778,8 @@
     <col width="14.375" bestFit="1" customWidth="1" style="14" min="10" max="10"/>
     <col width="39.125" bestFit="1" customWidth="1" style="14" min="11" max="11"/>
     <col width="39.125" bestFit="1" customWidth="1" style="4" min="12" max="12"/>
-    <col width="9" customWidth="1" style="4" min="13" max="14"/>
-    <col width="9" customWidth="1" style="4" min="15" max="16384"/>
+    <col width="9" customWidth="1" style="4" min="13" max="15"/>
+    <col width="9" customWidth="1" style="4" min="16" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customFormat="1" customHeight="1" s="2">
@@ -1028,6 +1040,11 @@
           <t>전투 보조 룬</t>
         </is>
       </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>skill_013</t>
+        </is>
+      </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
           <t>Independent</t>
@@ -1132,9 +1149,14 @@
           <t>공격속도 증가</t>
         </is>
       </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>skill_018</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>IndependentShared</t>
         </is>
       </c>
       <c r="H10" t="n">

--- a/Shared/XLS/Buff.xlsx
+++ b/Shared/XLS/Buff.xlsx
@@ -50,9 +50,6 @@
     <t>IndependentShared</t>
   </si>
   <si>
-    <t>스택마다 독립 인스턴스 + 수명은 공유(쌍검 공속)</t>
-  </si>
-  <si>
     <t>ActionBlockType</t>
   </si>
   <si>
@@ -212,9 +209,6 @@
     <t>기절! 받는 데미지 +100%</t>
   </si>
   <si>
-    <t>BUFF_DualBlades_AtkSpeedUp</t>
-  </si>
-  <si>
     <t>연속공격</t>
   </si>
   <si>
@@ -224,10 +218,19 @@
     <t>skill_018</t>
   </si>
   <si>
-    <t>SE_DualBlades_AtkSpeedUp_StatChange</t>
-  </si>
-  <si>
     <t>Independent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스택마다 독립 인스턴스 + 수명은 공유(대검 공속)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_GreatSword_AtkSpeedUp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_GreatSword_AtkSpeedUp_StatChange</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -742,7 +745,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -810,7 +813,7 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="12" customFormat="1">
@@ -821,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="7"/>
@@ -829,34 +832,34 @@
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
         <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>15</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
         <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
         <v>19</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -889,10 +892,10 @@
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>22</v>
       </c>
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
@@ -906,89 +909,89 @@
     </row>
     <row r="2" spans="1:13">
       <c r="B2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="G2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="H2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="I2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="J2" t="s">
         <v>30</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>31</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="M2" s="14" t="s">
         <v>33</v>
-      </c>
-      <c r="M2" s="14" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="B3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="D3" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="G3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="K3" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="14" t="s">
+      <c r="L3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>41</v>
-      </c>
       <c r="M3" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
         <v>42</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>44</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -1000,18 +1003,18 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
         <v>46</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>47</v>
-      </c>
-      <c r="D5" t="s">
-        <v>48</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -1023,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -1031,13 +1034,13 @@
     </row>
     <row r="6" spans="1:13">
       <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
         <v>50</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>51</v>
-      </c>
-      <c r="D6" t="s">
-        <v>52</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -1049,41 +1052,41 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="B7" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="E7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>56</v>
-      </c>
       <c r="G7" s="14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H7" s="14">
         <v>0</v>
       </c>
       <c r="L7" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="14" t="s">
         <v>57</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
         <v>59</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>60</v>
-      </c>
-      <c r="D8" t="s">
-        <v>61</v>
       </c>
       <c r="G8" t="s">
         <v>2</v>
@@ -1094,13 +1097,13 @@
     </row>
     <row r="9" spans="1:13">
       <c r="B9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" t="s">
         <v>62</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>63</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -1112,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -1121,21 +1124,21 @@
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" t="s">
         <v>65</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="D10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>68</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
@@ -1144,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
